--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_DP_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_DP_PYRAD/results.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.72 ± nan</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
